--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348683</v>
+        <v>120348690</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553998</v>
+        <v>553881</v>
       </c>
       <c r="R2" t="n">
-        <v>7017016</v>
+        <v>7016933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348698</v>
+        <v>120348679</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553881</v>
+        <v>553987</v>
       </c>
       <c r="R4" t="n">
-        <v>7016933</v>
+        <v>7017098</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348684</v>
+        <v>120348700</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554004</v>
+        <v>553972</v>
       </c>
       <c r="R5" t="n">
-        <v>7016997</v>
+        <v>7016986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348700</v>
+        <v>120348677</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553972</v>
+        <v>553887</v>
       </c>
       <c r="R6" t="n">
-        <v>7016986</v>
+        <v>7016874</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1169,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348682</v>
+        <v>120348684</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554013</v>
+        <v>554004</v>
       </c>
       <c r="R7" t="n">
-        <v>7017040</v>
+        <v>7016997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348696</v>
+        <v>120348708</v>
       </c>
       <c r="B8" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553743</v>
+        <v>553947</v>
       </c>
       <c r="R8" t="n">
-        <v>7016587</v>
+        <v>7016883</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348689</v>
+        <v>120348696</v>
       </c>
       <c r="B9" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553994</v>
+        <v>553743</v>
       </c>
       <c r="R9" t="n">
-        <v>7017141</v>
+        <v>7016587</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348690</v>
+        <v>120348698</v>
       </c>
       <c r="B10" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1613,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348709</v>
+        <v>120348685</v>
       </c>
       <c r="B11" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1629,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553793</v>
+        <v>553936</v>
       </c>
       <c r="R11" t="n">
-        <v>7016642</v>
+        <v>7016957</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1698,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348699</v>
+        <v>120348711</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553902</v>
+        <v>553681</v>
       </c>
       <c r="R12" t="n">
-        <v>7017017</v>
+        <v>7016435</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1832,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348676</v>
+        <v>120348682</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1862,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553807</v>
+        <v>554013</v>
       </c>
       <c r="R13" t="n">
-        <v>7016824</v>
+        <v>7017040</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1929,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348711</v>
+        <v>120348676</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1945,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1969,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553681</v>
+        <v>553807</v>
       </c>
       <c r="R14" t="n">
-        <v>7016435</v>
+        <v>7016824</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2009,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348695</v>
+        <v>120348681</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2052,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2076,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553686</v>
+        <v>554007</v>
       </c>
       <c r="R15" t="n">
-        <v>7016506</v>
+        <v>7017090</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2138,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348677</v>
+        <v>120348710</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2154,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2178,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553887</v>
+        <v>553804</v>
       </c>
       <c r="R16" t="n">
-        <v>7016874</v>
+        <v>7016554</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2218,7 +2233,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348708</v>
+        <v>120348683</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553947</v>
+        <v>553998</v>
       </c>
       <c r="R17" t="n">
-        <v>7016883</v>
+        <v>7017016</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2325,7 +2340,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2367,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348710</v>
+        <v>120348699</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2383,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2407,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553804</v>
+        <v>553902</v>
       </c>
       <c r="R18" t="n">
-        <v>7016554</v>
+        <v>7017017</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,11 +2443,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348681</v>
+        <v>120348695</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554007</v>
+        <v>553686</v>
       </c>
       <c r="R19" t="n">
-        <v>7017090</v>
+        <v>7016506</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2535,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348679</v>
+        <v>120348709</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553987</v>
+        <v>553793</v>
       </c>
       <c r="R20" t="n">
-        <v>7017098</v>
+        <v>7016642</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348685</v>
+        <v>120348689</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553936</v>
+        <v>553994</v>
       </c>
       <c r="R21" t="n">
-        <v>7016957</v>
+        <v>7017141</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348690</v>
+        <v>120348698</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348706</v>
+        <v>120348690</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553769</v>
+        <v>553881</v>
       </c>
       <c r="R3" t="n">
-        <v>7016676</v>
+        <v>7016933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348679</v>
+        <v>120348700</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553987</v>
+        <v>553972</v>
       </c>
       <c r="R4" t="n">
-        <v>7017098</v>
+        <v>7016986</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348700</v>
+        <v>120348685</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553972</v>
+        <v>553936</v>
       </c>
       <c r="R5" t="n">
-        <v>7016986</v>
+        <v>7016957</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348677</v>
+        <v>120348711</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553887</v>
+        <v>553681</v>
       </c>
       <c r="R6" t="n">
-        <v>7016874</v>
+        <v>7016435</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1168,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348708</v>
+        <v>120348681</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553947</v>
+        <v>554007</v>
       </c>
       <c r="R8" t="n">
-        <v>7016883</v>
+        <v>7017090</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348696</v>
+        <v>120348709</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553743</v>
+        <v>553793</v>
       </c>
       <c r="R9" t="n">
-        <v>7016587</v>
+        <v>7016642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348698</v>
+        <v>120348689</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553881</v>
+        <v>553994</v>
       </c>
       <c r="R10" t="n">
-        <v>7016933</v>
+        <v>7017141</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1618,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348685</v>
+        <v>120348677</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1658,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553936</v>
+        <v>553887</v>
       </c>
       <c r="R11" t="n">
-        <v>7016957</v>
+        <v>7016874</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348711</v>
+        <v>120348710</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1765,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553681</v>
+        <v>553804</v>
       </c>
       <c r="R12" t="n">
-        <v>7016435</v>
+        <v>7016554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348682</v>
+        <v>120348695</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554013</v>
+        <v>553686</v>
       </c>
       <c r="R13" t="n">
-        <v>7017040</v>
+        <v>7016506</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1908,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348676</v>
+        <v>120348706</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553807</v>
+        <v>553769</v>
       </c>
       <c r="R14" t="n">
-        <v>7016824</v>
+        <v>7016676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348681</v>
+        <v>120348683</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554007</v>
+        <v>553998</v>
       </c>
       <c r="R15" t="n">
-        <v>7017090</v>
+        <v>7017016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348710</v>
+        <v>120348696</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553804</v>
+        <v>553743</v>
       </c>
       <c r="R16" t="n">
-        <v>7016554</v>
+        <v>7016587</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2229,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,7 +2250,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348683</v>
+        <v>120348679</v>
       </c>
       <c r="B17" t="n">
         <v>57320</v>
@@ -2300,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553998</v>
+        <v>553987</v>
       </c>
       <c r="R17" t="n">
-        <v>7017016</v>
+        <v>7017098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2367,10 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348699</v>
+        <v>120348676</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2383,21 +2373,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2407,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553902</v>
+        <v>553807</v>
       </c>
       <c r="R18" t="n">
-        <v>7017017</v>
+        <v>7016824</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2443,6 +2433,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2469,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348695</v>
+        <v>120348708</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2485,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553686</v>
+        <v>553947</v>
       </c>
       <c r="R19" t="n">
-        <v>7016506</v>
+        <v>7016883</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2545,6 +2540,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348709</v>
+        <v>120348682</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553793</v>
+        <v>554013</v>
       </c>
       <c r="R20" t="n">
-        <v>7016642</v>
+        <v>7017040</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348689</v>
+        <v>120348699</v>
       </c>
       <c r="B21" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553994</v>
+        <v>553902</v>
       </c>
       <c r="R21" t="n">
-        <v>7017141</v>
+        <v>7017017</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -1516,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348689</v>
+        <v>120348677</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553994</v>
+        <v>553887</v>
       </c>
       <c r="R10" t="n">
-        <v>7017141</v>
+        <v>7016874</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348677</v>
+        <v>120348689</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553887</v>
+        <v>553994</v>
       </c>
       <c r="R11" t="n">
-        <v>7016874</v>
+        <v>7017141</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348698</v>
+        <v>120348677</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553881</v>
+        <v>553887</v>
       </c>
       <c r="R2" t="n">
-        <v>7016933</v>
+        <v>7016874</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348690</v>
+        <v>120348708</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553881</v>
+        <v>553947</v>
       </c>
       <c r="R3" t="n">
-        <v>7016933</v>
+        <v>7016883</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +858,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348700</v>
+        <v>120348690</v>
       </c>
       <c r="B4" t="n">
-        <v>79623</v>
+        <v>79624</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +905,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553972</v>
+        <v>553881</v>
       </c>
       <c r="R4" t="n">
-        <v>7016986</v>
+        <v>7016933</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348685</v>
+        <v>120348706</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553936</v>
+        <v>553769</v>
       </c>
       <c r="R5" t="n">
-        <v>7016957</v>
+        <v>7016676</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,7 +1071,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348711</v>
+        <v>120348683</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553681</v>
+        <v>553998</v>
       </c>
       <c r="R6" t="n">
-        <v>7016435</v>
+        <v>7017016</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1168,7 +1178,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1205,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348684</v>
+        <v>120348676</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1235,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554004</v>
+        <v>553807</v>
       </c>
       <c r="R7" t="n">
-        <v>7016997</v>
+        <v>7016824</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1275,7 +1285,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1312,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348681</v>
+        <v>120348689</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554007</v>
+        <v>553994</v>
       </c>
       <c r="R8" t="n">
-        <v>7017090</v>
+        <v>7017141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,11 +1388,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348709</v>
+        <v>120348698</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553793</v>
+        <v>553881</v>
       </c>
       <c r="R9" t="n">
-        <v>7016642</v>
+        <v>7016933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348677</v>
+        <v>120348685</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553887</v>
+        <v>553936</v>
       </c>
       <c r="R10" t="n">
-        <v>7016874</v>
+        <v>7016957</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348689</v>
+        <v>120348682</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553994</v>
+        <v>554013</v>
       </c>
       <c r="R11" t="n">
-        <v>7017141</v>
+        <v>7017040</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1699,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,10 +1730,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348710</v>
+        <v>120348700</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1741,21 +1746,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1765,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553804</v>
+        <v>553972</v>
       </c>
       <c r="R12" t="n">
-        <v>7016554</v>
+        <v>7016986</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1801,11 +1806,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,7 +1934,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348706</v>
+        <v>120348710</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553769</v>
+        <v>553804</v>
       </c>
       <c r="R14" t="n">
-        <v>7016676</v>
+        <v>7016554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2041,10 +2041,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348683</v>
+        <v>120348696</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553998</v>
+        <v>553743</v>
       </c>
       <c r="R15" t="n">
-        <v>7017016</v>
+        <v>7016587</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,11 +2117,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,10 +2143,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348696</v>
+        <v>120348711</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2164,21 +2159,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553743</v>
+        <v>553681</v>
       </c>
       <c r="R16" t="n">
-        <v>7016587</v>
+        <v>7016435</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2224,6 +2219,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348679</v>
+        <v>120348709</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553987</v>
+        <v>553793</v>
       </c>
       <c r="R17" t="n">
-        <v>7017098</v>
+        <v>7016642</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,7 +2357,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348676</v>
+        <v>120348684</v>
       </c>
       <c r="B18" t="n">
         <v>57320</v>
@@ -2397,10 +2397,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553807</v>
+        <v>554004</v>
       </c>
       <c r="R18" t="n">
-        <v>7016824</v>
+        <v>7016997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2437,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2464,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348708</v>
+        <v>120348699</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2480,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553947</v>
+        <v>553902</v>
       </c>
       <c r="R19" t="n">
-        <v>7016883</v>
+        <v>7017017</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2540,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,7 +2566,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348682</v>
+        <v>120348681</v>
       </c>
       <c r="B20" t="n">
         <v>57320</v>
@@ -2611,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554013</v>
+        <v>554007</v>
       </c>
       <c r="R20" t="n">
-        <v>7017040</v>
+        <v>7017090</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2651,7 +2646,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348699</v>
+        <v>120348679</v>
       </c>
       <c r="B21" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2694,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553902</v>
+        <v>553987</v>
       </c>
       <c r="R21" t="n">
-        <v>7017017</v>
+        <v>7017098</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2754,6 +2749,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348677</v>
+        <v>120348689</v>
       </c>
       <c r="B2" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553887</v>
+        <v>553994</v>
       </c>
       <c r="R2" t="n">
-        <v>7016874</v>
+        <v>7017141</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348708</v>
+        <v>120348676</v>
       </c>
       <c r="B3" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553947</v>
+        <v>553807</v>
       </c>
       <c r="R3" t="n">
-        <v>7016883</v>
+        <v>7016824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348690</v>
+        <v>120348681</v>
       </c>
       <c r="B4" t="n">
-        <v>79624</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553881</v>
+        <v>554007</v>
       </c>
       <c r="R4" t="n">
-        <v>7016933</v>
+        <v>7017090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348706</v>
+        <v>120348690</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553769</v>
+        <v>553881</v>
       </c>
       <c r="R5" t="n">
-        <v>7016676</v>
+        <v>7016933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348683</v>
+        <v>120348709</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553998</v>
+        <v>553793</v>
       </c>
       <c r="R6" t="n">
-        <v>7017016</v>
+        <v>7016642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348676</v>
+        <v>120348684</v>
       </c>
       <c r="B7" t="n">
         <v>57320</v>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553807</v>
+        <v>554004</v>
       </c>
       <c r="R7" t="n">
-        <v>7016824</v>
+        <v>7016997</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1312,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348689</v>
+        <v>120348682</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1328,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553994</v>
+        <v>554013</v>
       </c>
       <c r="R8" t="n">
-        <v>7017141</v>
+        <v>7017040</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1388,6 +1383,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348698</v>
+        <v>120348711</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553881</v>
+        <v>553681</v>
       </c>
       <c r="R9" t="n">
-        <v>7016933</v>
+        <v>7016435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,6 +1490,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,10 +1521,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348685</v>
+        <v>120348699</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1532,21 +1537,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1556,10 +1561,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553936</v>
+        <v>553902</v>
       </c>
       <c r="R10" t="n">
-        <v>7016957</v>
+        <v>7017017</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1592,11 +1597,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348682</v>
+        <v>120348700</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554013</v>
+        <v>553972</v>
       </c>
       <c r="R11" t="n">
-        <v>7017040</v>
+        <v>7016986</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348700</v>
+        <v>120348677</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553972</v>
+        <v>553887</v>
       </c>
       <c r="R12" t="n">
-        <v>7016986</v>
+        <v>7016874</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1806,6 +1801,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348695</v>
+        <v>120348679</v>
       </c>
       <c r="B13" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1848,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553686</v>
+        <v>553987</v>
       </c>
       <c r="R13" t="n">
-        <v>7016506</v>
+        <v>7017098</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,6 +1908,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348710</v>
+        <v>120348685</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553804</v>
+        <v>553936</v>
       </c>
       <c r="R14" t="n">
-        <v>7016554</v>
+        <v>7016957</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2019,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2143,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348711</v>
+        <v>120348698</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553681</v>
+        <v>553881</v>
       </c>
       <c r="R16" t="n">
-        <v>7016435</v>
+        <v>7016933</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,11 +2224,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2250,10 +2250,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348709</v>
+        <v>120348695</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2266,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2290,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553793</v>
+        <v>553686</v>
       </c>
       <c r="R17" t="n">
-        <v>7016642</v>
+        <v>7016506</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,11 +2326,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348684</v>
+        <v>120348708</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2373,21 +2368,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2397,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554004</v>
+        <v>553947</v>
       </c>
       <c r="R18" t="n">
-        <v>7016997</v>
+        <v>7016883</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2437,7 +2432,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348699</v>
+        <v>120348710</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553902</v>
+        <v>553804</v>
       </c>
       <c r="R19" t="n">
-        <v>7017017</v>
+        <v>7016554</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,6 +2535,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348681</v>
+        <v>120348706</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554007</v>
+        <v>553769</v>
       </c>
       <c r="R20" t="n">
-        <v>7017090</v>
+        <v>7016676</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,7 +2673,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348679</v>
+        <v>120348683</v>
       </c>
       <c r="B21" t="n">
         <v>57320</v>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553987</v>
+        <v>553998</v>
       </c>
       <c r="R21" t="n">
-        <v>7017098</v>
+        <v>7017016</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348689</v>
+        <v>120348711</v>
       </c>
       <c r="B2" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553994</v>
+        <v>553681</v>
       </c>
       <c r="R2" t="n">
-        <v>7017141</v>
+        <v>7016435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348676</v>
+        <v>120348706</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553807</v>
+        <v>553769</v>
       </c>
       <c r="R3" t="n">
-        <v>7016824</v>
+        <v>7016676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +862,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348681</v>
+        <v>120348682</v>
       </c>
       <c r="B4" t="n">
         <v>57320</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554007</v>
+        <v>554013</v>
       </c>
       <c r="R4" t="n">
-        <v>7017090</v>
+        <v>7017040</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +996,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348690</v>
+        <v>120348699</v>
       </c>
       <c r="B5" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553881</v>
+        <v>553902</v>
       </c>
       <c r="R5" t="n">
-        <v>7016933</v>
+        <v>7017017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348709</v>
+        <v>120348690</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1109,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553793</v>
+        <v>553881</v>
       </c>
       <c r="R6" t="n">
-        <v>7016642</v>
+        <v>7016933</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348684</v>
+        <v>120348709</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554004</v>
+        <v>553793</v>
       </c>
       <c r="R7" t="n">
-        <v>7016997</v>
+        <v>7016642</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack färska till äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,10 +1307,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348682</v>
+        <v>120348689</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1323,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554013</v>
+        <v>553994</v>
       </c>
       <c r="R8" t="n">
-        <v>7017040</v>
+        <v>7017141</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,11 +1383,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1414,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348711</v>
+        <v>120348695</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1430,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553681</v>
+        <v>553686</v>
       </c>
       <c r="R9" t="n">
-        <v>7016435</v>
+        <v>7016506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1485,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,7 +1511,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348699</v>
+        <v>120348696</v>
       </c>
       <c r="B10" t="n">
         <v>79623</v>
@@ -1561,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553902</v>
+        <v>553743</v>
       </c>
       <c r="R10" t="n">
-        <v>7017017</v>
+        <v>7016587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348700</v>
+        <v>120348683</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553972</v>
+        <v>553998</v>
       </c>
       <c r="R11" t="n">
-        <v>7016986</v>
+        <v>7017016</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1725,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348677</v>
+        <v>120348676</v>
       </c>
       <c r="B12" t="n">
         <v>57320</v>
@@ -1765,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553887</v>
+        <v>553807</v>
       </c>
       <c r="R12" t="n">
-        <v>7016874</v>
+        <v>7016824</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1805,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1832,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348679</v>
+        <v>120348681</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1872,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553987</v>
+        <v>554007</v>
       </c>
       <c r="R13" t="n">
-        <v>7017098</v>
+        <v>7017090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1912,7 +1907,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1939,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348685</v>
+        <v>120348710</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1955,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1979,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553936</v>
+        <v>553804</v>
       </c>
       <c r="R14" t="n">
-        <v>7016957</v>
+        <v>7016554</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2019,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348696</v>
+        <v>120348698</v>
       </c>
       <c r="B15" t="n">
         <v>79623</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553743</v>
+        <v>553881</v>
       </c>
       <c r="R15" t="n">
-        <v>7016587</v>
+        <v>7016933</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2148,7 +2143,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348698</v>
+        <v>120348700</v>
       </c>
       <c r="B16" t="n">
         <v>79623</v>
@@ -2188,10 +2183,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553881</v>
+        <v>553972</v>
       </c>
       <c r="R16" t="n">
-        <v>7016933</v>
+        <v>7016986</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2250,10 +2245,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348695</v>
+        <v>120348685</v>
       </c>
       <c r="B17" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2266,21 +2261,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2285,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553686</v>
+        <v>553936</v>
       </c>
       <c r="R17" t="n">
-        <v>7016506</v>
+        <v>7016957</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2326,6 +2321,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2352,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348708</v>
+        <v>120348684</v>
       </c>
       <c r="B18" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2368,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2392,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553947</v>
+        <v>554004</v>
       </c>
       <c r="R18" t="n">
-        <v>7016883</v>
+        <v>7016997</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2432,7 +2432,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,10 +2459,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348710</v>
+        <v>120348679</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2475,21 +2475,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2499,10 +2499,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553804</v>
+        <v>553987</v>
       </c>
       <c r="R19" t="n">
-        <v>7016554</v>
+        <v>7017098</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2566,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348706</v>
+        <v>120348677</v>
       </c>
       <c r="B20" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2582,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553769</v>
+        <v>553887</v>
       </c>
       <c r="R20" t="n">
-        <v>7016676</v>
+        <v>7016874</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348683</v>
+        <v>120348708</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553998</v>
+        <v>553947</v>
       </c>
       <c r="R21" t="n">
-        <v>7017016</v>
+        <v>7016883</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -1098,10 +1098,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348690</v>
+        <v>120348709</v>
       </c>
       <c r="B6" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553881</v>
+        <v>553793</v>
       </c>
       <c r="R6" t="n">
-        <v>7016933</v>
+        <v>7016642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,6 +1174,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348709</v>
+        <v>120348690</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79624</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553793</v>
+        <v>553881</v>
       </c>
       <c r="R7" t="n">
-        <v>7016642</v>
+        <v>7016933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,11 +1281,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348676</v>
+        <v>120348710</v>
       </c>
       <c r="B12" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553807</v>
+        <v>553804</v>
       </c>
       <c r="R12" t="n">
-        <v>7016824</v>
+        <v>7016554</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1827,7 +1827,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348681</v>
+        <v>120348676</v>
       </c>
       <c r="B13" t="n">
         <v>57320</v>
@@ -1867,10 +1867,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554007</v>
+        <v>553807</v>
       </c>
       <c r="R13" t="n">
-        <v>7017090</v>
+        <v>7016824</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1934,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348710</v>
+        <v>120348681</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1950,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1974,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553804</v>
+        <v>554007</v>
       </c>
       <c r="R14" t="n">
-        <v>7016554</v>
+        <v>7017090</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348711</v>
+        <v>120348695</v>
       </c>
       <c r="B2" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>553681</v>
+        <v>553686</v>
       </c>
       <c r="R2" t="n">
-        <v>7016435</v>
+        <v>7016506</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -889,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348682</v>
+        <v>120348689</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554013</v>
+        <v>553994</v>
       </c>
       <c r="R4" t="n">
-        <v>7017040</v>
+        <v>7017141</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -965,11 +960,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348699</v>
+        <v>120348677</v>
       </c>
       <c r="B5" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1012,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553902</v>
+        <v>553887</v>
       </c>
       <c r="R5" t="n">
-        <v>7017017</v>
+        <v>7016874</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348709</v>
+        <v>120348682</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1114,21 +1109,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553793</v>
+        <v>554013</v>
       </c>
       <c r="R6" t="n">
-        <v>7016642</v>
+        <v>7017040</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348690</v>
+        <v>120348699</v>
       </c>
       <c r="B7" t="n">
-        <v>79624</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553881</v>
+        <v>553902</v>
       </c>
       <c r="R7" t="n">
-        <v>7016933</v>
+        <v>7017017</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,10 +1302,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348689</v>
+        <v>120348710</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1323,21 +1318,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1347,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553994</v>
+        <v>553804</v>
       </c>
       <c r="R8" t="n">
-        <v>7017141</v>
+        <v>7016554</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,6 +1378,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1409,10 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348695</v>
+        <v>120348679</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1425,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553686</v>
+        <v>553987</v>
       </c>
       <c r="R9" t="n">
-        <v>7016506</v>
+        <v>7017098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,6 +1485,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,10 +1516,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348696</v>
+        <v>120348676</v>
       </c>
       <c r="B10" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1532,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553743</v>
+        <v>553807</v>
       </c>
       <c r="R10" t="n">
-        <v>7016587</v>
+        <v>7016824</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,6 +1592,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,7 +1623,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348683</v>
+        <v>120348681</v>
       </c>
       <c r="B11" t="n">
         <v>57320</v>
@@ -1653,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553998</v>
+        <v>554007</v>
       </c>
       <c r="R11" t="n">
-        <v>7017016</v>
+        <v>7017090</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,7 +1703,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1730,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348710</v>
+        <v>120348709</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1760,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553804</v>
+        <v>553793</v>
       </c>
       <c r="R12" t="n">
-        <v>7016554</v>
+        <v>7016642</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1827,10 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348676</v>
+        <v>120348711</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1843,21 +1853,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1867,10 +1877,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553807</v>
+        <v>553681</v>
       </c>
       <c r="R13" t="n">
-        <v>7016824</v>
+        <v>7016435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1907,7 +1917,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1934,10 +1944,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348681</v>
+        <v>120348698</v>
       </c>
       <c r="B14" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1950,21 +1960,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1974,10 +1984,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554007</v>
+        <v>553881</v>
       </c>
       <c r="R14" t="n">
-        <v>7017090</v>
+        <v>7016933</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,11 +2020,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2041,10 +2046,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348698</v>
+        <v>120348683</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2057,21 +2062,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2081,10 +2086,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553881</v>
+        <v>553998</v>
       </c>
       <c r="R15" t="n">
-        <v>7016933</v>
+        <v>7017016</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2117,6 +2122,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,10 +2153,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348700</v>
+        <v>120348708</v>
       </c>
       <c r="B16" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2159,21 +2169,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2183,10 +2193,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553972</v>
+        <v>553947</v>
       </c>
       <c r="R16" t="n">
-        <v>7016986</v>
+        <v>7016883</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2219,6 +2229,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2245,10 +2260,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348685</v>
+        <v>120348690</v>
       </c>
       <c r="B17" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2261,21 +2276,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2285,10 +2300,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553936</v>
+        <v>553881</v>
       </c>
       <c r="R17" t="n">
-        <v>7016957</v>
+        <v>7016933</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2321,11 +2336,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2352,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348684</v>
+        <v>120348700</v>
       </c>
       <c r="B18" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2368,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554004</v>
+        <v>553972</v>
       </c>
       <c r="R18" t="n">
-        <v>7016997</v>
+        <v>7016986</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2428,11 +2438,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2459,7 +2464,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348679</v>
+        <v>120348684</v>
       </c>
       <c r="B19" t="n">
         <v>57320</v>
@@ -2499,10 +2504,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553987</v>
+        <v>554004</v>
       </c>
       <c r="R19" t="n">
-        <v>7017098</v>
+        <v>7016997</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2539,7 +2544,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2566,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348677</v>
+        <v>120348696</v>
       </c>
       <c r="B20" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2582,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2606,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553887</v>
+        <v>553743</v>
       </c>
       <c r="R20" t="n">
-        <v>7016874</v>
+        <v>7016587</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2642,11 +2647,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2673,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348708</v>
+        <v>120348685</v>
       </c>
       <c r="B21" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2689,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2713,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553947</v>
+        <v>553936</v>
       </c>
       <c r="R21" t="n">
-        <v>7016883</v>
+        <v>7016957</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348706</v>
+        <v>120348711</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>553769</v>
+        <v>553681</v>
       </c>
       <c r="R3" t="n">
-        <v>7016676</v>
+        <v>7016435</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348689</v>
+        <v>120348684</v>
       </c>
       <c r="B4" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553994</v>
+        <v>554004</v>
       </c>
       <c r="R4" t="n">
-        <v>7017141</v>
+        <v>7016997</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348677</v>
+        <v>120348699</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553887</v>
+        <v>553902</v>
       </c>
       <c r="R5" t="n">
-        <v>7016874</v>
+        <v>7017017</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,11 +1067,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348682</v>
+        <v>120348676</v>
       </c>
       <c r="B6" t="n">
         <v>57320</v>
@@ -1133,10 +1133,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554013</v>
+        <v>553807</v>
       </c>
       <c r="R6" t="n">
-        <v>7017040</v>
+        <v>7016824</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348699</v>
+        <v>120348706</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>553902</v>
+        <v>553769</v>
       </c>
       <c r="R7" t="n">
-        <v>7017017</v>
+        <v>7016676</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1276,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1307,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348710</v>
+        <v>120348709</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1342,10 +1347,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553804</v>
+        <v>553793</v>
       </c>
       <c r="R8" t="n">
-        <v>7016554</v>
+        <v>7016642</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1409,10 +1414,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348679</v>
+        <v>120348690</v>
       </c>
       <c r="B9" t="n">
-        <v>57320</v>
+        <v>79624</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1425,21 +1430,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1454,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553987</v>
+        <v>553881</v>
       </c>
       <c r="R9" t="n">
-        <v>7017098</v>
+        <v>7016933</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1485,11 +1490,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1516,7 +1516,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348676</v>
+        <v>120348679</v>
       </c>
       <c r="B10" t="n">
         <v>57320</v>
@@ -1556,10 +1556,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553807</v>
+        <v>553987</v>
       </c>
       <c r="R10" t="n">
-        <v>7016824</v>
+        <v>7017098</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348681</v>
+        <v>120348698</v>
       </c>
       <c r="B11" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1639,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554007</v>
+        <v>553881</v>
       </c>
       <c r="R11" t="n">
-        <v>7017090</v>
+        <v>7016933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,11 +1699,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1730,10 +1725,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348709</v>
+        <v>120348682</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1746,21 +1741,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1770,10 +1765,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553793</v>
+        <v>554013</v>
       </c>
       <c r="R12" t="n">
-        <v>7016642</v>
+        <v>7017040</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1810,7 +1805,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1837,10 +1832,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348711</v>
+        <v>120348681</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1853,21 +1848,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1877,10 +1872,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>553681</v>
+        <v>554007</v>
       </c>
       <c r="R13" t="n">
-        <v>7016435</v>
+        <v>7017090</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1917,7 +1912,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1944,10 +1939,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120348698</v>
+        <v>120348689</v>
       </c>
       <c r="B14" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1960,21 +1955,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1984,10 +1979,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>553881</v>
+        <v>553994</v>
       </c>
       <c r="R14" t="n">
-        <v>7016933</v>
+        <v>7017141</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2046,7 +2041,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348683</v>
+        <v>120348677</v>
       </c>
       <c r="B15" t="n">
         <v>57320</v>
@@ -2086,10 +2081,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553998</v>
+        <v>553887</v>
       </c>
       <c r="R15" t="n">
-        <v>7017016</v>
+        <v>7016874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2126,7 +2121,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2153,10 +2148,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348708</v>
+        <v>120348685</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2169,21 +2164,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2193,10 +2188,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553947</v>
+        <v>553936</v>
       </c>
       <c r="R16" t="n">
-        <v>7016883</v>
+        <v>7016957</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2233,7 +2228,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2260,10 +2255,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348690</v>
+        <v>120348708</v>
       </c>
       <c r="B17" t="n">
-        <v>79624</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2276,21 +2271,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2300,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553881</v>
+        <v>553947</v>
       </c>
       <c r="R17" t="n">
-        <v>7016933</v>
+        <v>7016883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2336,6 +2331,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,10 +2362,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348700</v>
+        <v>120348683</v>
       </c>
       <c r="B18" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2378,21 +2378,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2402,10 +2402,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553972</v>
+        <v>553998</v>
       </c>
       <c r="R18" t="n">
-        <v>7016986</v>
+        <v>7017016</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2438,6 +2438,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2464,10 +2469,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348684</v>
+        <v>120348696</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2480,21 +2485,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2504,10 +2509,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554004</v>
+        <v>553743</v>
       </c>
       <c r="R19" t="n">
-        <v>7016997</v>
+        <v>7016587</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2540,11 +2545,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2571,10 +2571,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348696</v>
+        <v>120348710</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2587,21 +2587,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2611,10 +2611,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553743</v>
+        <v>553804</v>
       </c>
       <c r="R20" t="n">
-        <v>7016587</v>
+        <v>7016554</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2647,6 +2647,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2673,10 +2678,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348685</v>
+        <v>120348700</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2689,21 +2694,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2713,10 +2718,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553936</v>
+        <v>553972</v>
       </c>
       <c r="R21" t="n">
-        <v>7016957</v>
+        <v>7016986</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2749,11 +2754,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120348698</v>
+        <v>120348690</v>
       </c>
       <c r="B2" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120348682</v>
+        <v>120348706</v>
       </c>
       <c r="B3" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554013</v>
+        <v>553769</v>
       </c>
       <c r="R3" t="n">
-        <v>7017040</v>
+        <v>7016676</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +847,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,37 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120348695</v>
+        <v>120348707</v>
       </c>
       <c r="B4" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>553686</v>
+        <v>553776</v>
       </c>
       <c r="R4" t="n">
-        <v>7016506</v>
+        <v>7016756</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +945,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,19 +976,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120348710</v>
+        <v>120348708</v>
       </c>
       <c r="B5" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1026,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>553804</v>
+        <v>553947</v>
       </c>
       <c r="R5" t="n">
-        <v>7016554</v>
+        <v>7016883</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1093,37 +1078,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120348679</v>
+        <v>120348709</v>
       </c>
       <c r="B6" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1133,10 +1113,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>553987</v>
+        <v>553793</v>
       </c>
       <c r="R6" t="n">
-        <v>7017098</v>
+        <v>7016642</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1153,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120348681</v>
+        <v>120348710</v>
       </c>
       <c r="B7" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554007</v>
+        <v>553804</v>
       </c>
       <c r="R7" t="n">
-        <v>7017090</v>
+        <v>7016554</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1255,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1307,19 +1282,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120348709</v>
+        <v>120348711</v>
       </c>
       <c r="B8" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1347,10 +1317,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>553793</v>
+        <v>553681</v>
       </c>
       <c r="R8" t="n">
-        <v>7016642</v>
+        <v>7016435</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1414,15 +1384,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120348706</v>
+        <v>120348695</v>
       </c>
       <c r="B9" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1454,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>553769</v>
+        <v>553686</v>
       </c>
       <c r="R9" t="n">
-        <v>7016676</v>
+        <v>7016506</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1490,11 +1455,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1521,15 +1481,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120348677</v>
+        <v>120348696</v>
       </c>
       <c r="B10" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1537,21 +1492,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1561,10 +1516,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>553887</v>
+        <v>553743</v>
       </c>
       <c r="R10" t="n">
-        <v>7016874</v>
+        <v>7016587</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,11 +1552,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1628,15 +1578,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120348689</v>
+        <v>120348698</v>
       </c>
       <c r="B11" t="n">
-        <v>57488</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1644,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1668,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>553994</v>
+        <v>553881</v>
       </c>
       <c r="R11" t="n">
-        <v>7017141</v>
+        <v>7016933</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1730,15 +1675,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120348696</v>
+        <v>120348699</v>
       </c>
       <c r="B12" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1770,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>553743</v>
+        <v>553902</v>
       </c>
       <c r="R12" t="n">
-        <v>7016587</v>
+        <v>7017017</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1832,15 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120348684</v>
+        <v>120348700</v>
       </c>
       <c r="B13" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,21 +1783,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1872,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554004</v>
+        <v>553972</v>
       </c>
       <c r="R13" t="n">
-        <v>7016997</v>
+        <v>7016986</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1908,11 +1843,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2024-10-10</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack färska till äldre</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1942,12 +1872,7 @@
         <v>120348676</v>
       </c>
       <c r="B14" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,15 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120348700</v>
+        <v>120348677</v>
       </c>
       <c r="B15" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2062,21 +1982,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2086,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>553972</v>
+        <v>553887</v>
       </c>
       <c r="R15" t="n">
-        <v>7016986</v>
+        <v>7016874</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2122,6 +2042,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2148,15 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120348708</v>
+        <v>120348678</v>
       </c>
       <c r="B16" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2164,21 +2084,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2188,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>553947</v>
+        <v>553918</v>
       </c>
       <c r="R16" t="n">
-        <v>7016883</v>
+        <v>7017105</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2228,7 +2148,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2255,15 +2175,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120348683</v>
+        <v>120348679</v>
       </c>
       <c r="B17" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2295,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>553998</v>
+        <v>553987</v>
       </c>
       <c r="R17" t="n">
-        <v>7017016</v>
+        <v>7017098</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2362,15 +2277,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120348685</v>
+        <v>120348681</v>
       </c>
       <c r="B18" t="n">
-        <v>57335</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2402,10 +2312,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>553936</v>
+        <v>554007</v>
       </c>
       <c r="R18" t="n">
-        <v>7016957</v>
+        <v>7017090</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2469,15 +2379,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120348711</v>
+        <v>120348682</v>
       </c>
       <c r="B19" t="n">
-        <v>78564</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2485,21 +2390,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2509,10 +2414,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>553681</v>
+        <v>554013</v>
       </c>
       <c r="R19" t="n">
-        <v>7016435</v>
+        <v>7017040</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2549,7 +2454,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2576,15 +2481,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120348699</v>
+        <v>120348683</v>
       </c>
       <c r="B20" t="n">
-        <v>79645</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2592,21 +2492,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2616,10 +2516,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>553902</v>
+        <v>553998</v>
       </c>
       <c r="R20" t="n">
-        <v>7017017</v>
+        <v>7017016</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2652,6 +2552,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2678,15 +2583,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120348690</v>
+        <v>120348684</v>
       </c>
       <c r="B21" t="n">
-        <v>79646</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2694,21 +2594,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2718,10 +2618,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>553881</v>
+        <v>554004</v>
       </c>
       <c r="R21" t="n">
-        <v>7016933</v>
+        <v>7016997</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2756,6 +2656,11 @@
           <t>2024-10-10</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack färska till äldre</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2777,6 +2682,205 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120348685</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>553936</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7016957</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120348689</v>
+      </c>
+      <c r="B23" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Höksberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>553994</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7017141</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-10</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 38169-2024 artfynd.xlsx
+++ b/artfynd/A 38169-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348690</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348706</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348707</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348708</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348709</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1279,6 +1309,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348710</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,6 +1416,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348711</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,6 +1518,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348695</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1575,6 +1620,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348696</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1672,6 +1722,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348698</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348699</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1866,6 +1926,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348700</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348676</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348677</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348678</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2274,6 +2354,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348679</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2376,6 +2461,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348681</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2478,6 +2568,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348682</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2580,6 +2675,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348683</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2682,6 +2782,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348684</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2784,6 +2889,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348685</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2881,8 +2991,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120348689</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>